--- a/data/fasilitas_kesehatan.xlsx
+++ b/data/fasilitas_kesehatan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8943049E-7CE1-45FA-BC2F-3328174358C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD869C32-7C03-4D16-ABDC-C4AE75737839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FC893FD-77BE-4229-B4B6-2DAA2D953E5F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="357">
   <si>
     <t>Id</t>
   </si>
@@ -261,357 +261,51 @@
     <t>rawat jalan, rawat inap, instalasi gawat darurat (IGD), laboratorium, radiologi, farmasi, serta pelayanan penunjang medis lainnya,</t>
   </si>
   <si>
-    <t>00,00-23,59 WIB</t>
-  </si>
-  <si>
-    <t>-7,757387001873601</t>
-  </si>
-  <si>
-    <t>110,40372260012042</t>
-  </si>
-  <si>
-    <t>Jl, Ring Road Utara No,160, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>4,7/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/8TnFtQJi6E1CaLNTA</t>
-  </si>
-  <si>
-    <t>images\FK001,jpg</t>
-  </si>
-  <si>
-    <t>-7,770033634050055</t>
-  </si>
-  <si>
-    <t>110,43269859457864</t>
-  </si>
-  <si>
-    <t>Jl, Selokan Mataram, Meguwo, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
-  </si>
-  <si>
-    <t>4,0/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/1H9LhxzMtv64yXoD8</t>
-  </si>
-  <si>
     <t>images\FK002.jpg</t>
   </si>
   <si>
-    <t>-7,753128236973273</t>
-  </si>
-  <si>
-    <t>110,40578096366399</t>
-  </si>
-  <si>
-    <t>Jl, Manggis No,6, Gempol, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>4,1/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/M2DmUGq6Lb4fXi887</t>
-  </si>
-  <si>
-    <t>images\FK003,png</t>
-  </si>
-  <si>
-    <t>-7,783202202286065</t>
-  </si>
-  <si>
-    <t>110,37817418108473</t>
-  </si>
-  <si>
-    <t>Jl, Jend, Sudirman No,70, Kotabaru, Kec, Gondokusuman, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55224</t>
-  </si>
-  <si>
-    <t>4,8/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Vk1UaybocLxyF5Yw7</t>
-  </si>
-  <si>
-    <t>images\FK004,jpg</t>
-  </si>
-  <si>
     <t>Pemeriksaan umum, konsultasi dokter, rawat jalan</t>
   </si>
   <si>
-    <t>-7,749745155319422</t>
-  </si>
-  <si>
-    <t>110,40927081444552</t>
-  </si>
-  <si>
-    <t>jln swadaya 1 karangasem gempol, RT,04/RW,12, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>4,5/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/XgYtpt8ryzqD8AkLA</t>
-  </si>
-  <si>
-    <t>images\FK005,jpg</t>
-  </si>
-  <si>
     <t>Layanan kesehatan umum 24 jam, konsultasi dokter</t>
   </si>
   <si>
-    <t>-7,766014020359649</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 110,38225684420644</t>
-  </si>
-  <si>
-    <t>Jl, Agro No,38C, Kocoran, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,6/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/kKiNjvD2KJAeGVPV6</t>
-  </si>
-  <si>
-    <t>images\FK006,jpg</t>
-  </si>
-  <si>
     <t>Penjualan obat, konsultasi obat</t>
   </si>
   <si>
-    <t>08,00-20,30</t>
-  </si>
-  <si>
-    <t>-7,768463429285144</t>
-  </si>
-  <si>
-    <t>110,39121087116467</t>
-  </si>
-  <si>
-    <t>Jl, Affandi CT X No,16, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/qLqPjq81wHZqcJ5S8</t>
-  </si>
-  <si>
-    <t>images\FK007,jpg</t>
-  </si>
-  <si>
     <t>Penjualan obat, layanan resep</t>
   </si>
   <si>
-    <t>08,00-21,00</t>
-  </si>
-  <si>
-    <t>-7,752829612238244</t>
-  </si>
-  <si>
-    <t>110,38219637601044</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang KM,6 No,30, Manggung, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,2/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/SqgPajwbHizYcSJu6</t>
-  </si>
-  <si>
-    <t>images\FK008,jpg</t>
-  </si>
-  <si>
-    <t>07,30-22,00</t>
-  </si>
-  <si>
-    <t>-7,782761552095657</t>
-  </si>
-  <si>
-    <t>110,40601933690814</t>
-  </si>
-  <si>
-    <t>Jl, Laksda Adisucipto Km 6 No,15, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/xbPDVPw6Fe5SFdtc7</t>
-  </si>
-  <si>
-    <t>images\FK009,jpg</t>
-  </si>
-  <si>
     <t>Penjualan obat, layanan farmasi</t>
   </si>
   <si>
-    <t>07,00-21,00</t>
-  </si>
-  <si>
-    <t>-7,784418272722908</t>
-  </si>
-  <si>
-    <t>110,39966138293197</t>
-  </si>
-  <si>
-    <t>Komplek Polri, Jl, Nogorojo blok A1, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55198</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/2i6wAoz24HrWx1JW9</t>
-  </si>
-  <si>
-    <t>images\FK010,jpg</t>
-  </si>
-  <si>
     <t>Penjualan obat, konsultasi farmasi</t>
   </si>
   <si>
-    <t>06,00-22,00</t>
-  </si>
-  <si>
-    <t>-7,768662196639806</t>
-  </si>
-  <si>
-    <t>110,38987746468595</t>
-  </si>
-  <si>
     <t>Gg, Endra No,27, RT,/RW/RW,013/005, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
-    <t>3,5/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/mbC1NPM9U34KDYus6</t>
-  </si>
-  <si>
-    <t>images\FK011,jpg</t>
-  </si>
-  <si>
     <t>Layanan apotek 24 jam, penjualan obat</t>
   </si>
   <si>
-    <t>-7,782768432099361</t>
-  </si>
-  <si>
-    <t>110,39745634060283</t>
-  </si>
-  <si>
-    <t>Jl, Laksda Adisucipto No,150 A, Papringan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/c7V2vzZY4uNawn1S9</t>
-  </si>
-  <si>
-    <t>images\FK012,jpg</t>
-  </si>
-  <si>
-    <t>07,00-22,00</t>
-  </si>
-  <si>
-    <t>-7,774333978500341</t>
-  </si>
-  <si>
-    <t>110,41571232710868</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari No,88, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,7/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/DxbMbvnuCY6KidC49</t>
-  </si>
-  <si>
-    <t>images\FK013,jfif</t>
-  </si>
-  <si>
-    <t>-7,769040096252525</t>
-  </si>
-  <si>
-    <t>110,40200444938012</t>
-  </si>
-  <si>
-    <t>Jl, Wahid Hasyim, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,3/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/KcmcSCptgPdkQBTs6</t>
-  </si>
-  <si>
-    <t>images\FK014,jpg</t>
-  </si>
-  <si>
     <t>Apotek Unisia 24 Condongcatur</t>
   </si>
   <si>
-    <t xml:space="preserve">07,00-22,00 </t>
-  </si>
-  <si>
-    <t>-7,7595999858181575</t>
-  </si>
-  <si>
-    <t>110,41256162105965</t>
-  </si>
-  <si>
-    <t>Depan FE UII, Jl, Prawiro Kuat, Ngringin, Condongcatur, Kec, Depok, Yogyakarta, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>5,0/5</t>
-  </si>
-  <si>
     <t>(0811)30862021</t>
   </si>
   <si>
-    <t>https://maps,app,goo,gl/bhV722T2KbGQQKZ37</t>
-  </si>
-  <si>
-    <t>images\FK015,jpg</t>
-  </si>
-  <si>
     <t>Apotek SS</t>
   </si>
   <si>
-    <t>-7,76563812041298</t>
-  </si>
-  <si>
-    <t>110,41093083808957</t>
-  </si>
-  <si>
-    <t>Jl, Seturan Raya No,3, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
     <t>(0274)486618</t>
   </si>
   <si>
-    <t>https://maps,app,goo,gl/yDeY9nHthTNAqnJ9A</t>
-  </si>
-  <si>
-    <t>images\FK016,jpg</t>
-  </si>
-  <si>
     <t>Apotek Mafaza Kledokan</t>
   </si>
   <si>
-    <t>-7,7763283347203505</t>
-  </si>
-  <si>
-    <t>110,40850553587747</t>
-  </si>
-  <si>
-    <t>C Jl, Raya Kledokan No,6, Tempel, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
     <t>(0823)42306767</t>
   </si>
   <si>
-    <t>https://maps,app,goo,gl/6E7axsaCBssf6qSN8</t>
-  </si>
-  <si>
-    <t>images\FK017,jpg</t>
-  </si>
-  <si>
     <t>RSU Sakina Idaman</t>
   </si>
   <si>
@@ -624,9 +318,6 @@
     <t>https://maps.app.goo.gl/D8BEoe6yV55Jq2Lm9</t>
   </si>
   <si>
-    <t>images\FK018,jpg</t>
-  </si>
-  <si>
     <t>FK019</t>
   </si>
   <si>
@@ -639,9 +330,6 @@
     <t>https://maps.app.goo.gl/11upKF5QySQPoVk86</t>
   </si>
   <si>
-    <t>images\FK019,jpg</t>
-  </si>
-  <si>
     <t>FK020</t>
   </si>
   <si>
@@ -654,9 +342,6 @@
     <t>https://maps.app.goo.gl/o9nppm1zFCSGGqrG9</t>
   </si>
   <si>
-    <t>images\FK020,jpg</t>
-  </si>
-  <si>
     <t>FK021</t>
   </si>
   <si>
@@ -672,9 +357,6 @@
     <t>https://maps.app.goo.gl/xUkX5VYC1eGwJT1F7</t>
   </si>
   <si>
-    <t>images\FK021,jpg</t>
-  </si>
-  <si>
     <t>FK022</t>
   </si>
   <si>
@@ -687,9 +369,6 @@
     <t>https://maps.app.goo.gl/4bJ33oBrU7xWsNny5</t>
   </si>
   <si>
-    <t>images\FK022,jpg</t>
-  </si>
-  <si>
     <t>FK023</t>
   </si>
   <si>
@@ -705,9 +384,6 @@
     <t>https://maps.app.goo.gl/4T8Qcr5RYqEmqYcy6</t>
   </si>
   <si>
-    <t>images\FK023,jpg</t>
-  </si>
-  <si>
     <t>FK024</t>
   </si>
   <si>
@@ -723,9 +399,6 @@
     <t>https://maps.app.goo.gl/qm1optJ4jLjePebS9</t>
   </si>
   <si>
-    <t>images\FK024,jpg</t>
-  </si>
-  <si>
     <t>FK025</t>
   </si>
   <si>
@@ -846,9 +519,6 @@
     <t>Senin-Sabtu</t>
   </si>
   <si>
-    <t>07,00-11,00 WIB</t>
-  </si>
-  <si>
     <t>Jl. Lely III, Perumnas Condong Catur, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
   </si>
   <si>
@@ -867,9 +537,6 @@
     <t>mengatasi keluhan cedera, nyeri kronis otot-tulang (spt : leher, bahu, pinggang,lutut), massage-recovery, rehabilitasi pasca operasi orthopedi, konsultasi gizi dan kebugaran.</t>
   </si>
   <si>
-    <t>08,00-21,00 WIB</t>
-  </si>
-  <si>
     <t>Jl. Ring Road Utara No.416, Perumnas Condong Catur, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
@@ -888,9 +555,6 @@
     <t>pencegahan, diagnosis, dan pengobatan berbagai kondisi medis yang mempengaruhi anak-anak.</t>
   </si>
   <si>
-    <t>07,00-20,00 WIB</t>
-  </si>
-  <si>
     <t>Jl. Perumnas No.207, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
@@ -960,9 +624,6 @@
     <t>Klinik Pratama Panasea</t>
   </si>
   <si>
-    <t>07,00-21,00 WIB</t>
-  </si>
-  <si>
     <t>Jl. Kenari No.89, Muja Muju, Kec. Umbulharjo, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55167</t>
   </si>
   <si>
@@ -1135,6 +796,315 @@
   </si>
   <si>
     <t>(0274)4461804</t>
+  </si>
+  <si>
+    <t>00.00-23.59 WIB</t>
+  </si>
+  <si>
+    <t>08.00-20.30</t>
+  </si>
+  <si>
+    <t>08.00-21.00</t>
+  </si>
+  <si>
+    <t>07.30-22.00</t>
+  </si>
+  <si>
+    <t>07.00-21.00</t>
+  </si>
+  <si>
+    <t>06.00-22.00</t>
+  </si>
+  <si>
+    <t>07.00-22.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07.00-22.00 </t>
+  </si>
+  <si>
+    <t>07.00-11.00 WIB</t>
+  </si>
+  <si>
+    <t>07.00-20.00 WIB</t>
+  </si>
+  <si>
+    <t>07.00-21.00 WIB</t>
+  </si>
+  <si>
+    <t>-7.757387001873601</t>
+  </si>
+  <si>
+    <t>-7.770033634050055</t>
+  </si>
+  <si>
+    <t>-7.753128236973273</t>
+  </si>
+  <si>
+    <t>-7.783202202286065</t>
+  </si>
+  <si>
+    <t>-7.749745155319422</t>
+  </si>
+  <si>
+    <t>-7.766014020359649</t>
+  </si>
+  <si>
+    <t>-7.768463429285144</t>
+  </si>
+  <si>
+    <t>-7.752829612238244</t>
+  </si>
+  <si>
+    <t>-7.782761552095657</t>
+  </si>
+  <si>
+    <t>-7.784418272722908</t>
+  </si>
+  <si>
+    <t>-7.768662196639806</t>
+  </si>
+  <si>
+    <t>-7.782768432099361</t>
+  </si>
+  <si>
+    <t>-7.774333978500341</t>
+  </si>
+  <si>
+    <t>-7.769040096252525</t>
+  </si>
+  <si>
+    <t>-7.7595999858181575</t>
+  </si>
+  <si>
+    <t>-7.76563812041298</t>
+  </si>
+  <si>
+    <t>-7.7763283347203505</t>
+  </si>
+  <si>
+    <t>110.40372260012042</t>
+  </si>
+  <si>
+    <t>110.43269859457864</t>
+  </si>
+  <si>
+    <t>110.40578096366399</t>
+  </si>
+  <si>
+    <t>110.37817418108473</t>
+  </si>
+  <si>
+    <t>110.40927081444552</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 110.38225684420644</t>
+  </si>
+  <si>
+    <t>110.39121087116467</t>
+  </si>
+  <si>
+    <t>110.38219637601044</t>
+  </si>
+  <si>
+    <t>110.40601933690814</t>
+  </si>
+  <si>
+    <t>110.39966138293197</t>
+  </si>
+  <si>
+    <t>110.38987746468595</t>
+  </si>
+  <si>
+    <t>110.39745634060283</t>
+  </si>
+  <si>
+    <t>110.41571232710868</t>
+  </si>
+  <si>
+    <t>110.40200444938012</t>
+  </si>
+  <si>
+    <t>110.41256162105965</t>
+  </si>
+  <si>
+    <t>110.41093083808957</t>
+  </si>
+  <si>
+    <t>110.40850553587747</t>
+  </si>
+  <si>
+    <t>Jl. Ring Road Utara No,160, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Selokan Mataram, Meguwo, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>Jl. Manggis No,6, Gempol, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>Jl. Jend, Sudirman No,70, Kotabaru, Kec, Gondokusuman, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55224</t>
+  </si>
+  <si>
+    <t>Jl. Agro No,38C, Kocoran, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Affandi CT X No,16, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang KM,6 No,30, Manggung, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Laksda Adisucipto Km 6 No,15, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Komplek Polri, Jl. Nogorojo blok A1, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55198</t>
+  </si>
+  <si>
+    <t>Jl. Laksda Adisucipto No,150 A, Papringan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari No,88, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Wahid Hasyim, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Depan FE UII, Jl. Prawiro Kuat, Ngringin, Condongcatur, Kec, Depok, Yogyakarta, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Seturan Raya No,3, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>C Jl. Raya Kledokan No,6, Tempel, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. swadaya 1 karangasem gempol, RT,04/RW,12, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>4.7/5.0</t>
+  </si>
+  <si>
+    <t>5.0/5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8TnFtQJi6E1CaLNTA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1H9LhxzMtv64yXoD8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/M2DmUGq6Lb4fXi887</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Vk1UaybocLxyF5Yw7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XgYtpt8ryzqD8AkLA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kKiNjvD2KJAeGVPV6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qLqPjq81wHZqcJ5S8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SqgPajwbHizYcSJu6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xbPDVPw6Fe5SFdtc7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2i6wAoz24HrWx1JW9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mbC1NPM9U34KDYus6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/c7V2vzZY4uNawn1S9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DxbMbvnuCY6KidC49</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KcmcSCptgPdkQBTs6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/bhV722T2KbGQQKZ37</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/yDeY9nHthTNAqnJ9A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6E7axsaCBssf6qSN8</t>
+  </si>
+  <si>
+    <t>images\FK001.jpg</t>
+  </si>
+  <si>
+    <t>images\FK003.png</t>
+  </si>
+  <si>
+    <t>images\FK004.jpg</t>
+  </si>
+  <si>
+    <t>images\FK005.jpg</t>
+  </si>
+  <si>
+    <t>images\FK006.jpg</t>
+  </si>
+  <si>
+    <t>images\FK007.jpg</t>
+  </si>
+  <si>
+    <t>images\FK008.jpg</t>
+  </si>
+  <si>
+    <t>images\FK009.jpg</t>
+  </si>
+  <si>
+    <t>images\FK010.jpg</t>
+  </si>
+  <si>
+    <t>images\FK011.jpg</t>
+  </si>
+  <si>
+    <t>images\FK012.jpg</t>
+  </si>
+  <si>
+    <t>images\FK013.jfif</t>
+  </si>
+  <si>
+    <t>images\FK014.jpg</t>
+  </si>
+  <si>
+    <t>images\FK015.jpg</t>
+  </si>
+  <si>
+    <t>images\FK016.jpg</t>
+  </si>
+  <si>
+    <t>images\FK017.jpg</t>
+  </si>
+  <si>
+    <t>images\FK018.jpg</t>
+  </si>
+  <si>
+    <t>images\FK019.jpg</t>
+  </si>
+  <si>
+    <t>images\FK020.jpg</t>
+  </si>
+  <si>
+    <t>images\FK021.jpg</t>
+  </si>
+  <si>
+    <t>images\FK022.jpg</t>
+  </si>
+  <si>
+    <t>images\FK023.jpg</t>
+  </si>
+  <si>
+    <t>images\FK024.jpg</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1239,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1310,15 +1280,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1329,11 +1295,14 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1657,7 +1626,7 @@
     <col min="3" max="3" width="255.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="128.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.21875" bestFit="1" customWidth="1"/>
@@ -1722,31 +1691,31 @@
         <v>14</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>76</v>
+        <v>265</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>81</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.6">
@@ -1763,31 +1732,31 @@
         <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>84</v>
+        <v>300</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>86</v>
+        <v>318</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.6">
@@ -1804,31 +1773,31 @@
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>90</v>
+        <v>301</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>92</v>
+        <v>319</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>93</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6">
@@ -1845,31 +1814,31 @@
         <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>96</v>
+        <v>302</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>98</v>
+        <v>320</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>99</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6">
@@ -1880,37 +1849,37 @@
         <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>101</v>
+        <v>269</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>103</v>
+        <v>314</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>39</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>106</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6">
@@ -1921,37 +1890,37 @@
         <v>42</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>110</v>
+        <v>303</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>43</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>113</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6">
@@ -1962,37 +1931,37 @@
         <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>116</v>
+        <v>271</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>118</v>
+        <v>304</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>47</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>120</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6">
@@ -2003,37 +1972,37 @@
         <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>122</v>
+        <v>256</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>123</v>
+        <v>272</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>124</v>
+        <v>289</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>125</v>
+        <v>305</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>51</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>127</v>
+        <v>324</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>128</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6">
@@ -2050,31 +2019,31 @@
         <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>130</v>
+        <v>273</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>131</v>
+        <v>290</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>132</v>
+        <v>306</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>55</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>133</v>
+        <v>325</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>134</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6">
@@ -2085,37 +2054,37 @@
         <v>58</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>137</v>
+        <v>274</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>138</v>
+        <v>291</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>139</v>
+        <v>307</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>140</v>
+        <v>326</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>141</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6">
@@ -2126,37 +2095,37 @@
         <v>61</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>143</v>
+        <v>259</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>144</v>
+        <v>275</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>145</v>
+        <v>292</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>62</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>148</v>
+        <v>327</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>149</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6">
@@ -2167,37 +2136,37 @@
         <v>64</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>151</v>
+        <v>276</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>65</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="L13" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="M13" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.6">
@@ -2214,31 +2183,31 @@
         <v>14</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>157</v>
+        <v>277</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>158</v>
+        <v>294</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>159</v>
+        <v>309</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>69</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>161</v>
+        <v>329</v>
       </c>
       <c r="L14" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="M14" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6">
@@ -2249,37 +2218,37 @@
         <v>71</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>163</v>
+        <v>278</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>164</v>
+        <v>295</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>72</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>167</v>
+        <v>330</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>168</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6">
@@ -2287,7 +2256,7 @@
         <v>60</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>68</v>
@@ -2296,31 +2265,31 @@
         <v>14</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>172</v>
+        <v>296</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>174</v>
+        <v>316</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>176</v>
+        <v>331</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>177</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6">
@@ -2328,7 +2297,7 @@
         <v>63</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>68</v>
@@ -2337,31 +2306,31 @@
         <v>14</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>179</v>
+        <v>280</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>181</v>
+        <v>312</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>183</v>
+        <v>332</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>184</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6">
@@ -2369,7 +2338,7 @@
         <v>66</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>68</v>
@@ -2378,31 +2347,31 @@
         <v>14</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>143</v>
+        <v>259</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>186</v>
+        <v>281</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>188</v>
+        <v>313</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>174</v>
+        <v>316</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>190</v>
+        <v>333</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>191</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6">
@@ -2410,1039 +2379,1039 @@
         <v>70</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>192</v>
+        <v>90</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="14">
-        <v>-7767080231137650</v>
-      </c>
-      <c r="G19" s="14">
-        <v>1.10367971799999E+16</v>
+        <v>254</v>
+      </c>
+      <c r="F19" s="26">
+        <v>-7.7670802311376503</v>
+      </c>
+      <c r="G19" s="26">
+        <v>110.367971799999</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>33</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>346</v>
+        <v>233</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>195</v>
+        <v>93</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>196</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6">
       <c r="A20" s="4" t="s">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="14">
-        <v>-7768329279995170</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1.10373538573018E+16</v>
+        <v>254</v>
+      </c>
+      <c r="F20" s="26">
+        <v>-7.7683292799951698</v>
+      </c>
+      <c r="G20" s="26">
+        <v>110.373538573018</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>347</v>
+        <v>234</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>201</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6">
       <c r="A21" s="4" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>203</v>
+      <c r="C21" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="14">
-        <v>-777691839542124</v>
-      </c>
-      <c r="G21" s="14">
-        <v>110376169</v>
+        <v>254</v>
+      </c>
+      <c r="F21" s="26">
+        <v>-7.77691839542124</v>
+      </c>
+      <c r="G21" s="26">
+        <v>110.376169</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>15</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>348</v>
+        <v>235</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>205</v>
+        <v>101</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>206</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6">
       <c r="A22" s="4" t="s">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>209</v>
+        <v>103</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>104</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="14">
-        <v>-7783107500127860</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1.10390824555818E+16</v>
+        <v>254</v>
+      </c>
+      <c r="F22" s="26">
+        <v>-7.7831075001278602</v>
+      </c>
+      <c r="G22" s="26">
+        <v>110.390824555818</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>19</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>349</v>
+        <v>236</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>211</v>
+        <v>106</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>212</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6">
       <c r="A23" s="4" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>209</v>
+        <v>108</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="18">
-        <v>-7793733146002060</v>
-      </c>
-      <c r="G23" s="18">
-        <v>1.10391974444181E+16</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="I23" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="27">
+        <v>-7.7937331460020598</v>
+      </c>
+      <c r="G23" s="27">
+        <v>110.391974444181</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="K23" s="20" t="s">
-        <v>216</v>
+      <c r="J23" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>217</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6">
       <c r="A24" s="4" t="s">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>220</v>
+        <v>112</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>113</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="18">
-        <v>-774701758624274</v>
-      </c>
-      <c r="G24" s="18">
-        <v>1.10425070585396E+16</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="I24" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" s="27">
+        <v>-7.7470175862427402</v>
+      </c>
+      <c r="G24" s="27">
+        <v>110.425070585396</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="K24" s="20" t="s">
-        <v>222</v>
+      <c r="J24" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>115</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>223</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6">
       <c r="A25" s="4" t="s">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>226</v>
+        <v>118</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="18">
-        <v>-7770716702855060</v>
-      </c>
-      <c r="G25" s="18">
-        <v>1.10415832615345E+16</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="I25" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="F25" s="27">
+        <v>-7.7707167028550597</v>
+      </c>
+      <c r="G25" s="27">
+        <v>110.415832615345</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="I25" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="K25" s="20" t="s">
-        <v>228</v>
+      <c r="J25" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>229</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6">
       <c r="A26" s="4" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="B26" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" s="27">
+        <v>-7.7279713721929504</v>
+      </c>
+      <c r="G26" s="27">
+        <v>110.399538673018</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="L26" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="18">
-        <v>-7727971372192950</v>
-      </c>
-      <c r="G26" s="18">
-        <v>1.10399538673018E+16</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="K26" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="L26" s="10" t="s">
-        <v>344</v>
-      </c>
       <c r="M26" s="4" t="s">
-        <v>235</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6">
       <c r="A27" s="4" t="s">
-        <v>236</v>
+        <v>127</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>238</v>
+        <v>128</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="18">
-        <v>-7797465677717290</v>
-      </c>
-      <c r="G27" s="18">
-        <v>1.10410335499999E+16</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="I27" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" s="27">
+        <v>-7.7974656777172902</v>
+      </c>
+      <c r="G27" s="27">
+        <v>110.41033549999899</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="J27" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="K27" s="20" t="s">
-        <v>240</v>
+      <c r="J27" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>131</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>241</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6">
       <c r="A28" s="4" t="s">
-        <v>242</v>
+        <v>133</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>244</v>
+        <v>134</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="F28" s="18">
-        <v>-7756422594538750</v>
-      </c>
-      <c r="G28" s="18">
-        <v>1.10400673955818E+16</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="I28" s="17" t="s">
+      <c r="E28" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="27">
+        <v>-7.7564225945387504</v>
+      </c>
+      <c r="G28" s="27">
+        <v>110.40067395581799</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I28" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="20" t="s">
-        <v>247</v>
+      <c r="J28" s="17"/>
+      <c r="K28" s="18" t="s">
+        <v>138</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>248</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6">
       <c r="A29" s="4" t="s">
-        <v>249</v>
+        <v>140</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>251</v>
+        <v>141</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>142</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="18">
-        <v>-7777710367190850</v>
-      </c>
-      <c r="G29" s="18">
-        <v>1.10386913484654E+16</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I29" s="17" t="s">
+      <c r="E29" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29" s="27">
+        <v>-7.7777103671908501</v>
+      </c>
+      <c r="G29" s="27">
+        <v>110.386913484654</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I29" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J29" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="K29" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="L29" s="17" t="s">
-        <v>344</v>
+      <c r="J29" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>254</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6">
       <c r="A30" s="4" t="s">
-        <v>255</v>
+        <v>146</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>256</v>
+      <c r="C30" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="18">
-        <v>-7783053390067110</v>
-      </c>
-      <c r="G30" s="18">
-        <v>1.10378260015345E+16</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="I30" s="17" t="s">
+      <c r="E30" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F30" s="27">
+        <v>-7.7830533900671099</v>
+      </c>
+      <c r="G30" s="27">
+        <v>110.37826001534501</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="I30" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J30" s="19" t="s">
+      <c r="J30" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K30" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="L30" s="17" t="s">
-        <v>344</v>
+      <c r="K30" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>259</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6">
       <c r="A31" s="4" t="s">
-        <v>260</v>
+        <v>151</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>262</v>
+        <v>152</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="18">
-        <v>-7785402520969320</v>
-      </c>
-      <c r="G31" s="18">
-        <v>1.10376847957672E+16</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="I31" s="17" t="s">
+      <c r="E31" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" s="27">
+        <v>-7.7854025209693196</v>
+      </c>
+      <c r="G31" s="27">
+        <v>110.376847957672</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="I31" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J31" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="K31" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>344</v>
+      <c r="J31" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>265</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.6">
       <c r="A32" s="4" t="s">
-        <v>266</v>
+        <v>157</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>268</v>
+        <v>158</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="F32" s="18">
-        <v>-7756447217229270</v>
-      </c>
-      <c r="G32" s="18">
-        <v>1.10408118384654E+16</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="I32" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F32" s="27">
+        <v>-7.7564472172292698</v>
+      </c>
+      <c r="G32" s="27">
+        <v>110.408118384654</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="I32" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J32" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="K32" s="20" t="s">
-        <v>272</v>
+      <c r="J32" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>162</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>273</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.6">
       <c r="A33" s="4" t="s">
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>276</v>
+        <v>165</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="F33" s="18">
-        <v>-7759697127029020</v>
-      </c>
-      <c r="G33" s="18">
-        <v>1.10406640244181E+16</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="I33" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F33" s="27">
+        <v>-7.7596971270290203</v>
+      </c>
+      <c r="G33" s="27">
+        <v>110.40664024418101</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="I33" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="J33" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="K33" s="20" t="s">
-        <v>279</v>
+      <c r="J33" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>168</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>280</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.6">
       <c r="A34" s="4" t="s">
-        <v>281</v>
+        <v>170</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>283</v>
+        <v>171</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>172</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="F34" s="18">
-        <v>-7761034019432400</v>
-      </c>
-      <c r="G34" s="18">
-        <v>1.10406946473018E+16</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="K34" s="20" t="s">
-        <v>287</v>
+        <v>160</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="F34" s="27">
+        <v>-7.7610340194324001</v>
+      </c>
+      <c r="G34" s="27">
+        <v>110.406946473018</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>175</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15.6">
       <c r="A35" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>291</v>
+        <v>177</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>179</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F35" s="25">
-        <v>-7748230720655770</v>
-      </c>
-      <c r="G35" s="25">
-        <v>1.10434279655818E+16</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="I35" s="22" t="s">
+      <c r="E35" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F35" s="28">
+        <v>-7.7482307206557701</v>
+      </c>
+      <c r="G35" s="28">
+        <v>110.434279655818</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J35" s="26"/>
-      <c r="K35" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="L35" s="22" t="s">
-        <v>344</v>
+      <c r="J35" s="23"/>
+      <c r="K35" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>231</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>294</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15.6">
       <c r="A36" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>297</v>
+        <v>183</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>185</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="25">
-        <v>-7739402177953790</v>
-      </c>
-      <c r="G36" s="25">
-        <v>1103925487</v>
-      </c>
-      <c r="H36" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="I36" s="22" t="s">
+      <c r="E36" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F36" s="28">
+        <v>-7.7394021779537896</v>
+      </c>
+      <c r="G36" s="28">
+        <v>110.39254870000001</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="J36" s="26" t="s">
-        <v>360</v>
-      </c>
-      <c r="K36" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="L36" s="22" t="s">
-        <v>344</v>
+      <c r="J36" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="K36" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>231</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>300</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="15.6">
       <c r="A37" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>107</v>
+        <v>189</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>77</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>75</v>
+      <c r="E37" s="20" t="s">
+        <v>254</v>
       </c>
       <c r="F37" s="28">
-        <v>-7752708215524190</v>
-      </c>
-      <c r="G37" s="25">
-        <v>1.10384244342327E+16</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="I37" s="22" t="s">
+        <v>-7.7527082155241898</v>
+      </c>
+      <c r="G37" s="28">
+        <v>110.38424434232699</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="I37" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J37" s="26"/>
-      <c r="K37" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="L37" s="22" t="s">
-        <v>344</v>
+      <c r="J37" s="23"/>
+      <c r="K37" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>231</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.6">
       <c r="A38" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="C38" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F38" s="28">
+        <v>-7.8016898914058102</v>
+      </c>
+      <c r="G38" s="28">
+        <v>110.395526101854</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="K38" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="L38" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="F38" s="25">
-        <v>-780168989140581</v>
-      </c>
-      <c r="G38" s="25">
-        <v>1.10395526101854E+16</v>
-      </c>
-      <c r="H38" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="I38" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="K38" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>345</v>
-      </c>
       <c r="M38" s="4" t="s">
-        <v>311</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.6">
       <c r="A39" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>314</v>
+        <v>199</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>201</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="F39" s="25">
-        <v>-7788540681959050</v>
-      </c>
-      <c r="G39" s="25">
-        <v>1.10375229884654E+16</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="I39" s="22" t="s">
+      <c r="E39" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F39" s="28">
+        <v>-7.7885406819590504</v>
+      </c>
+      <c r="G39" s="28">
+        <v>110.375229884654</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="I39" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J39" s="26" t="s">
-        <v>362</v>
-      </c>
-      <c r="K39" s="27" t="s">
-        <v>317</v>
+      <c r="J39" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="K39" s="24" t="s">
+        <v>204</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>318</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6">
       <c r="A40" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B40" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="C40" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="28">
+        <v>-7.7859217107404204</v>
+      </c>
+      <c r="G40" s="28">
+        <v>110.39440355529899</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="K40" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D40" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="F40" s="25">
-        <v>-778592171074042</v>
-      </c>
-      <c r="G40" s="25">
-        <v>1103944035552990</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="I40" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="J40" s="26" t="s">
-        <v>363</v>
-      </c>
-      <c r="K40" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>345</v>
-      </c>
       <c r="M40" s="4" t="s">
-        <v>324</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6">
       <c r="A41" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="F41" s="25">
-        <v>-7753517169544080</v>
-      </c>
-      <c r="G41" s="25">
+        <v>212</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F41" s="28">
+        <v>-7.7535171695440797</v>
+      </c>
+      <c r="G41" s="28">
         <v>1.10434012315345E+16</v>
       </c>
-      <c r="H41" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="I41" s="22" t="s">
+      <c r="H41" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="I41" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="J41" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="K41" s="27" t="s">
-        <v>330</v>
+      <c r="J41" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="K41" s="24" t="s">
+        <v>217</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>331</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6">
       <c r="A42" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="F42" s="25">
-        <v>-7752340592228910</v>
-      </c>
-      <c r="G42" s="25">
-        <v>1104484104827990</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="I42" s="29">
+        <v>219</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="F42" s="28">
+        <v>-7.7523405922289097</v>
+      </c>
+      <c r="G42" s="28">
+        <v>110.44841048279901</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="I42" s="25">
         <v>46146</v>
       </c>
-      <c r="J42" s="26" t="s">
-        <v>365</v>
-      </c>
-      <c r="K42" s="27" t="s">
-        <v>337</v>
+      <c r="J42" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="K42" s="24" t="s">
+        <v>224</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>338</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.6">
       <c r="A43" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F43" s="25">
-        <v>-775968664937294</v>
-      </c>
-      <c r="G43" s="25">
-        <v>1.10433089257672E+16</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>341</v>
-      </c>
-      <c r="I43" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="28">
+        <v>-7.7596866493729397</v>
+      </c>
+      <c r="G43" s="28">
+        <v>110.43308925767199</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I43" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="J43" s="26" t="s">
-        <v>366</v>
-      </c>
-      <c r="K43" s="27" t="s">
-        <v>342</v>
-      </c>
-      <c r="L43" s="22" t="s">
-        <v>344</v>
+      <c r="J43" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="K43" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>231</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>343</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" xr:uid="{AE505C74-4A2D-400C-BFF4-5CD2F66D97F1}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{E7410802-D031-42B9-AB9B-CFD2E18AF19C}"/>
-    <hyperlink ref="K4" r:id="rId3" xr:uid="{3D42429A-50CD-47D1-8A2D-03619630598C}"/>
-    <hyperlink ref="K5" r:id="rId4" xr:uid="{005A1E56-0684-49D5-8B45-8290FCFA0D5E}"/>
-    <hyperlink ref="K6" r:id="rId5" xr:uid="{C9D89F6E-0A1B-43A2-B9E2-4736E488A1AF}"/>
-    <hyperlink ref="K7" r:id="rId6" xr:uid="{3E7ABB3A-EF59-421A-8EF6-BCE0816FE11E}"/>
-    <hyperlink ref="K8" r:id="rId7" xr:uid="{95C9454B-AA31-45DB-8EEB-4BD504264B00}"/>
-    <hyperlink ref="K9" r:id="rId8" xr:uid="{48D8C714-A247-4D0F-856E-BA3C5E7AC3AF}"/>
-    <hyperlink ref="K10" r:id="rId9" xr:uid="{D4B469F8-3656-4251-B930-4D23728F0124}"/>
-    <hyperlink ref="K11" r:id="rId10" xr:uid="{6B08BD55-514F-43B1-9246-892E10D83E27}"/>
-    <hyperlink ref="K12" r:id="rId11" xr:uid="{D831AF1E-83BA-4295-9D44-B47E023AE49F}"/>
-    <hyperlink ref="K13" r:id="rId12" xr:uid="{7478F165-3E72-44BA-9D8E-03B28AC39B58}"/>
-    <hyperlink ref="K14" r:id="rId13" xr:uid="{C72DF656-BE6B-4B0B-A574-BF0B739357D4}"/>
-    <hyperlink ref="K15" r:id="rId14" xr:uid="{74C1CC14-F6C5-4312-BFC0-4D6CDF015089}"/>
-    <hyperlink ref="K16" r:id="rId15" xr:uid="{C79B034B-0E92-4C84-9363-D870652EB8E8}"/>
-    <hyperlink ref="K17" r:id="rId16" xr:uid="{57BA1980-6CE4-46A7-B615-9C1334CD3EA7}"/>
-    <hyperlink ref="K18" r:id="rId17" xr:uid="{83300F22-C569-4EB8-8A0D-C9E408452FFF}"/>
+    <hyperlink ref="K2" r:id="rId1" display="https://maps,app,goo,gl/8TnFtQJi6E1CaLNTA" xr:uid="{AE505C74-4A2D-400C-BFF4-5CD2F66D97F1}"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://maps,app,goo,gl/1H9LhxzMtv64yXoD8" xr:uid="{E7410802-D031-42B9-AB9B-CFD2E18AF19C}"/>
+    <hyperlink ref="K4" r:id="rId3" display="https://maps,app,goo,gl/M2DmUGq6Lb4fXi887" xr:uid="{3D42429A-50CD-47D1-8A2D-03619630598C}"/>
+    <hyperlink ref="K5" r:id="rId4" display="https://maps,app,goo,gl/Vk1UaybocLxyF5Yw7" xr:uid="{005A1E56-0684-49D5-8B45-8290FCFA0D5E}"/>
+    <hyperlink ref="K6" r:id="rId5" display="https://maps,app,goo,gl/XgYtpt8ryzqD8AkLA" xr:uid="{C9D89F6E-0A1B-43A2-B9E2-4736E488A1AF}"/>
+    <hyperlink ref="K7" r:id="rId6" display="https://maps,app,goo,gl/kKiNjvD2KJAeGVPV6" xr:uid="{3E7ABB3A-EF59-421A-8EF6-BCE0816FE11E}"/>
+    <hyperlink ref="K8" r:id="rId7" display="https://maps,app,goo,gl/qLqPjq81wHZqcJ5S8" xr:uid="{95C9454B-AA31-45DB-8EEB-4BD504264B00}"/>
+    <hyperlink ref="K9" r:id="rId8" display="https://maps,app,goo,gl/SqgPajwbHizYcSJu6" xr:uid="{48D8C714-A247-4D0F-856E-BA3C5E7AC3AF}"/>
+    <hyperlink ref="K10" r:id="rId9" display="https://maps,app,goo,gl/xbPDVPw6Fe5SFdtc7" xr:uid="{D4B469F8-3656-4251-B930-4D23728F0124}"/>
+    <hyperlink ref="K11" r:id="rId10" display="https://maps,app,goo,gl/2i6wAoz24HrWx1JW9" xr:uid="{6B08BD55-514F-43B1-9246-892E10D83E27}"/>
+    <hyperlink ref="K12" r:id="rId11" display="https://maps,app,goo,gl/mbC1NPM9U34KDYus6" xr:uid="{D831AF1E-83BA-4295-9D44-B47E023AE49F}"/>
+    <hyperlink ref="K13" r:id="rId12" display="https://maps,app,goo,gl/c7V2vzZY4uNawn1S9" xr:uid="{7478F165-3E72-44BA-9D8E-03B28AC39B58}"/>
+    <hyperlink ref="K14" r:id="rId13" display="https://maps,app,goo,gl/DxbMbvnuCY6KidC49" xr:uid="{C72DF656-BE6B-4B0B-A574-BF0B739357D4}"/>
+    <hyperlink ref="K15" r:id="rId14" display="https://maps,app,goo,gl/KcmcSCptgPdkQBTs6" xr:uid="{74C1CC14-F6C5-4312-BFC0-4D6CDF015089}"/>
+    <hyperlink ref="K16" r:id="rId15" display="https://maps,app,goo,gl/bhV722T2KbGQQKZ37" xr:uid="{C79B034B-0E92-4C84-9363-D870652EB8E8}"/>
+    <hyperlink ref="K17" r:id="rId16" display="https://maps,app,goo,gl/yDeY9nHthTNAqnJ9A" xr:uid="{57BA1980-6CE4-46A7-B615-9C1334CD3EA7}"/>
+    <hyperlink ref="K18" r:id="rId17" display="https://maps,app,goo,gl/6E7axsaCBssf6qSN8" xr:uid="{83300F22-C569-4EB8-8A0D-C9E408452FFF}"/>
     <hyperlink ref="K19" r:id="rId18" xr:uid="{9FA5FD7D-68C3-4C66-BD2E-0DACF37740E2}"/>
     <hyperlink ref="K20" r:id="rId19" xr:uid="{49F617AC-F98B-4A0F-9266-6BEC9A484CF4}"/>
     <hyperlink ref="K21" r:id="rId20" xr:uid="{96444D1F-1E39-4B42-9B03-2C6CDA2E05D5}"/>
